--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MINNESOTA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MINNESOTA_2014.xlsx
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C82">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C212">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C543">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C609">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C630">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C993">
